--- a/data/trans_orig/IQ12A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas (tasa de respuesta: 97,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,32 +716,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 9,49</t>
+          <t>3,16; 9,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,39</t>
+          <t>2,31; 6,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,93</t>
+          <t>1,8; 3,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,56</t>
+          <t>2,24; 5,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,89</t>
+          <t>2,21; 4,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,48</t>
+          <t>1,83; 6,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +751,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 10,33</t>
+          <t>5,42; 10,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,34</t>
+          <t>2,97; 6,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,48</t>
+          <t>2,54; 5,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,91</t>
+          <t>2,08; 3,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 8,82</t>
+          <t>4,65; 8,61</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,12</t>
+          <t>2,69; 4,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,11</t>
+          <t>2,67; 4,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,75</t>
+          <t>2,61; 4,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 4,98</t>
+          <t>3,53; 4,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,9</t>
+          <t>2,9; 4,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,14</t>
+          <t>2,83; 4,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,79</t>
+          <t>2,35; 3,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,97</t>
+          <t>4,07; 6,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 4,51</t>
+          <t>3,01; 4,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 3,88</t>
+          <t>2,86; 3,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,93</t>
+          <t>2,64; 3,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 5,37</t>
+          <t>4,05; 5,37</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,29</t>
+          <t>1,65; 4,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,34</t>
+          <t>2,66; 5,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,32</t>
+          <t>2,4; 5,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,65</t>
+          <t>3,23; 6,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 8,52</t>
+          <t>3,12; 8,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,34</t>
+          <t>2,51; 7,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,47</t>
+          <t>2,49; 5,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,02</t>
+          <t>3,02; 7,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,87</t>
+          <t>2,76; 6,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,35</t>
+          <t>2,89; 5,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,93</t>
+          <t>2,68; 4,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,26</t>
+          <t>3,41; 5,96</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,75</t>
+          <t>2,96; 4,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,2</t>
+          <t>2,94; 4,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,25</t>
+          <t>2,65; 4,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,98</t>
+          <t>3,69; 4,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,05</t>
+          <t>3,18; 4,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,39</t>
+          <t>2,98; 4,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,82</t>
+          <t>2,58; 4,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,12</t>
+          <t>4,42; 6,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 4,49</t>
+          <t>3,26; 4,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,04</t>
+          <t>3,08; 4,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,76</t>
+          <t>2,76; 3,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,35</t>
+          <t>4,24; 5,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ12A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas (tasa de respuesta: 97,76%)</t>
+          <t>Tiempo medio en días que limitaron su actividad en las últimas 2 semanas por dolores o síntomas (tasa de respuesta: 97,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,32 +716,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 9,05</t>
+          <t>3,17; 9,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,51</t>
+          <t>2,16; 6,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,07</t>
+          <t>1,8; 3,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,6</t>
+          <t>2,0; 5,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,92</t>
+          <t>2,15; 4,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,86</t>
+          <t>1,83; 6,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +751,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 10,3</t>
+          <t>5,39; 10,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,7</t>
+          <t>2,95; 6,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,66</t>
+          <t>2,47; 5,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,94</t>
+          <t>2,05; 3,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,61</t>
+          <t>4,75; 8,67</t>
         </is>
       </c>
     </row>
@@ -856,22 +856,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,97</t>
+          <t>2,63; 5,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,18</t>
+          <t>2,61; 4,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,87</t>
+          <t>2,53; 4,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 4,96</t>
+          <t>3,57; 4,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,27 +881,27 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,25</t>
+          <t>2,8; 4,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,95</t>
+          <t>2,36; 3,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,05</t>
+          <t>4,07; 6,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,54</t>
+          <t>3,01; 4,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 3,8</t>
+          <t>2,84; 3,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,05; 5,37</t>
+          <t>4,05; 5,32</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,34</t>
+          <t>1,6; 4,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,43</t>
+          <t>2,6; 5,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,22</t>
+          <t>2,46; 5,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,62</t>
+          <t>3,28; 6,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,36</t>
+          <t>3,23; 8,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,02</t>
+          <t>2,52; 7,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,83</t>
+          <t>2,53; 7,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,34</t>
+          <t>2,98; 6,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,08</t>
+          <t>2,75; 6,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,32</t>
+          <t>2,92; 5,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,71</t>
+          <t>2,66; 4,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,96</t>
+          <t>3,47; 6,08</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,68</t>
+          <t>2,83; 4,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,17</t>
+          <t>2,89; 4,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,23</t>
+          <t>2,67; 4,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 4,95</t>
+          <t>3,67; 4,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,91</t>
+          <t>3,22; 4,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,42</t>
+          <t>2,97; 4,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,0</t>
+          <t>2,53; 3,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,1</t>
+          <t>4,36; 6,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,46</t>
+          <t>3,29; 4,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,07</t>
+          <t>3,12; 4,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,84</t>
+          <t>2,76; 3,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,38</t>
+          <t>4,24; 5,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ12A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Estudios-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,71</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,48</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7,92</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,73</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,31</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,04</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,15</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,71</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,48</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,86</t>
+          <t>3,96</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,55</t>
+          <t>6,6</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 9,01</t>
+          <t>2,14; 4,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,31</t>
+          <t>1,92; 7,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,01</t>
+          <t>2,0; 7,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,53</t>
+          <t>5,5; 10,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,8</t>
+          <t>3,15; 9,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,75</t>
+          <t>2,35; 6,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 7,0</t>
+          <t>1,8; 2,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 10,11</t>
+          <t>1,98; 5,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,33</t>
+          <t>2,97; 6,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,55</t>
+          <t>2,48; 5,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,78</t>
+          <t>2,06; 3,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,67</t>
+          <t>4,74; 8,99</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,66</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,37</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,96</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,04</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,68</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,25</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,38</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,27</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,66</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,37</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,96</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,65</t>
+          <t>4,68</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,1</t>
+          <t>2,87; 4,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,15</t>
+          <t>2,76; 4,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,81</t>
+          <t>2,34; 3,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,98</t>
+          <t>4,11; 6,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 4,84</t>
+          <t>2,77; 5,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,21</t>
+          <t>2,62; 4,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 3,84</t>
+          <t>2,59; 4,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,04</t>
+          <t>3,5; 4,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,5</t>
+          <t>3,03; 4,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,95</t>
+          <t>2,89; 3,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 3,94</t>
+          <t>2,63; 3,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,05; 5,32</t>
+          <t>4,11; 5,42</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,39</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,65</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,6</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,53</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,72</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,38</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,4</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,39</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,65</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>4,17</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,13</t>
+          <t>3,36; 8,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,24</t>
+          <t>2,66; 7,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,09</t>
+          <t>2,51; 6,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,94</t>
+          <t>3,13; 7,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,27</t>
+          <t>1,72; 4,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,16</t>
+          <t>2,53; 5,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,09</t>
+          <t>2,51; 5,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,83</t>
+          <t>3,17; 6,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,03</t>
+          <t>2,75; 5,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,43</t>
+          <t>2,89; 5,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,67</t>
+          <t>2,7; 4,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,08</t>
+          <t>3,44; 6,13</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,95</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,59</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,29</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,66</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,46</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,26</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,25</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,95</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>4,2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,8</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,75</t>
+          <t>3,22; 5,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,18</t>
+          <t>2,99; 4,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,15</t>
+          <t>2,54; 3,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 4,92</t>
+          <t>4,49; 6,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 4,91</t>
+          <t>2,94; 4,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 4,38</t>
+          <t>2,87; 4,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,89</t>
+          <t>2,65; 4,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,11</t>
+          <t>3,63; 4,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,58</t>
+          <t>3,23; 4,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,04</t>
+          <t>3,11; 4,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,83</t>
+          <t>2,77; 3,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,41</t>
+          <t>4,25; 5,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ12A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en días que limitaron su actividad en las últimas 2 semanas por dolores o síntomas (tasa de respuesta: 97,76%)</t>
+          <t>Tiempo medio en días que los menores limitaron su actividad en las últimas 2 semanas por dolores o síntomas (tasa de respuesta: 97,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,71</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,48</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,92</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,11</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,73</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,31</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3,96</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4,14</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3,72</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2,63</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,6</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.149320644261604</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.706639144519065</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.478804658775974</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7.921379427955993</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>5.112284481003</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>3.734776738015769</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>2.312519073629439</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>3.963212320081419</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>4.143965407899892</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>3.722706958202888</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>2.628808684504101</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>6.600638276077467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2,14; 4,89</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,92; 7,48</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2,0; 7,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5,5; 10,45</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,15; 9,49</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,35; 6,39</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,8; 2,93</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1,98; 5,7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2,97; 6,34</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2,48; 5,48</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2,06; 3,91</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>4,74; 8,99</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2.137520049563816</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1.915631316480179</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>5.499812493793383</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>3.154404500161381</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>2.350833804287852</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.796172000954341</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1.978690173993624</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>2.967380011640276</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>2.478375311396975</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>2.063589641376537</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>4.739170751748629</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.888331079175707</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.477720661858535</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10.45123602316325</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>9.491343185639543</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>6.393090716093866</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>2.934155775190851</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>5.701900021201027</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>6.34029646493232</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>5.476251748878899</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>3.90946417311125</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>8.989516633554274</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,66</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,37</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,96</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,04</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,68</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,38</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4,23</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3,67</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3,32</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3,16</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,68</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2,87; 4,9</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2,76; 4,14</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2,34; 3,79</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4,11; 6,09</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,77; 5,12</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,62; 4,11</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,59; 4,75</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3,5; 4,95</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3,03; 4,51</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2,89; 3,88</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2,63; 3,93</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,11; 5,42</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.657367374409391</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.368161933702953</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.964742437842837</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>5.043569172998324</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>3.683476758456744</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>3.254832059243857</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>3.37909628478259</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>4.233898272585211</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>3.66975994381817</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>3.319310530317106</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>3.163990229864498</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>4.67912724168866</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,39</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,65</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,6</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,53</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,72</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,38</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4,17</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>4,07</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3,99</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3,48</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>4,39</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>2.868856148586323</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2.763162291234426</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2.339793847008003</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>4.112342623903464</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>2.769061101278005</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>2.620082711478179</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>2.594039865163414</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>3.500342606077283</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>3.03462032041941</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>2.889680051566789</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>2.629705107002148</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>4.109525502695639</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>3,36; 8,52</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2,66; 7,34</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2,51; 6,47</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3,13; 7,12</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 4,29</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2,53; 5,34</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,51; 5,32</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3,17; 6,28</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2,75; 5,87</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2,89; 5,35</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2,7; 4,93</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>3,44; 6,13</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.897645071679954</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.137084331315022</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.786664018860105</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>6.091693215215613</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>5.124320219028737</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>4.107399025449087</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>4.745540893382544</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>4.951640714946898</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>4.514152055474163</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>3.876500861459681</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>3.929178066858614</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>5.422599646903531</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,95</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,66</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,46</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,26</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4,2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3,81</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,8</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>5.399356042712287</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4.392643753466442</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.654126182548372</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4.602746449904459</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>2.528918126903398</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>3.717761950125711</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>3.383762854014373</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>4.168294953743676</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>4.067811970483745</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>3.99406985972611</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>3.484119997110462</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>4.390209818725872</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>3,22; 5,05</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2,99; 4,39</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2,54; 3,82</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4,49; 6,23</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,94; 4,75</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,87; 4,2</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,65; 4,25</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3,63; 4,9</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3,23; 4,49</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3,11; 4,04</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2,77; 3,76</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>4,25; 5,38</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>3.36175844479084</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2.662864899806308</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2.507071180954346</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>3.126040558276709</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.720810960652982</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>2.525978900401781</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>2.509708095603227</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>3.172931572873121</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>2.749076764408812</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>2.886671777453761</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>2.697653977515715</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>3.443967317760759</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.521940589221312</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.341873629611928</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.468171752205233</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.121471895174063</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>4.294369589452159</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>5.340564304988345</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>5.322391309068479</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>6.282098030896859</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>5.865389539327171</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>5.345200882135186</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>4.93284605439867</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>6.125855419744802</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3.945601916730845</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.588834497697063</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>3.133645839672639</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>5.2883898255871</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>3.656725791927583</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>3.456844234535392</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>3.264182514215749</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>4.196507506838844</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>3.807920160023901</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>3.524737585550751</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>3.20405118490479</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>4.799125101621544</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>3.216835100523757</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>2.98630270680005</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>2.537059761609317</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>4.491646449014863</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>2.93737531074011</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>2.872547917331249</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>2.654237545863394</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>3.630459632788607</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>3.232162117499079</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>3.106832931488398</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>2.766593329066177</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>4.251364057267459</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.051663667690388</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.394134864994804</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.816646597527908</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.234195483667308</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>4.747348062115237</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>4.197378411003905</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>4.248348263941926</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>4.903035894506758</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>4.487814821461741</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>4.039193618632256</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>3.75975515804398</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>5.378420792859535</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
